--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,54 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -572,10 +590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,23 +630,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -677,8 +724,11 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -692,6 +742,9 @@
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -716,7 +769,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -739,10 +792,10 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
@@ -756,7 +809,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1079,10 +1132,8 @@
           <t>Sunjeet lama</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841451281</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841451281</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1148,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9808074911</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9808074911</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1166,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.71621</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.71621</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1172,55 +1219,267 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L53-5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.368</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.36799999999999</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 35m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381154</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9815730689</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9886262513</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:45:39 AM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:02:07 PM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.71748</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Near CHABAHIL PLAZA, Ring Road Chowk, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>samjhanagurung696@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>20:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L13-7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.3476</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 35m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 16m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -804,7 +804,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1334,10 +1334,8 @@
           <t>Anil Kumar</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9815730689</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9815730689</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1352,10 +1350,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9886262513</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9886262513</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1372,10 +1368,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.71748</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.71748</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1431,25 +1425,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L13-7</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.3476</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.3476</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,54 +528,72 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -722,13 +746,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>2</v>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -738,13 +765,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -758,12 +788,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -771,10 +801,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -798,19 +828,19 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1473,6 +1503,650 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.69469</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Maitighar Mandala -11, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>sagarsaridhungana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>21:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.32052</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:32 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381073</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Dhungana</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841141788</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:40:01 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:37:49 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.69469</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Maitighar Mandala -11, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>sagarsaridhungana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>21:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.32052</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 57m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381115</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Surya Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9863593473</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:30:32 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9863593473</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:13:54 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:30:32 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.703184</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>ASPHODEL PUBLIC SCHOOL - Private educational institution P83G+2XM Kathmandu 44600, Bagmati, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>suryathapa4301@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.32805</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -759,22 +759,41 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>4</v>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -834,7 +853,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1570,10 +1589,8 @@
           <t>Sagar Dhungana</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1588,10 +1605,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1608,10 +1623,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.69469</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.69469</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1667,25 +1680,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.32052</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.32052</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1786,10 +1795,8 @@
           <t>Sagar Dhungana</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1804,10 +1811,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9841141788</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9841141788</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1824,10 +1829,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.69469</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.69469</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1883,25 +1886,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.32052</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.32052</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -2002,10 +2001,8 @@
           <t>Surya Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9863593473</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9863593473</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2020,10 +2017,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9863593473</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9863593473</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -2040,10 +2035,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.703184</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.703184</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2095,47 +2088,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>CDB206</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.32805</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.32805</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2144,6 +2133,114 @@
       <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -580,18 +580,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -675,10 +693,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -702,14 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,6 +754,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -749,13 +773,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>4</v>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +800,10 @@
       <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -787,13 +817,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -807,13 +840,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -837,7 +870,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -848,18 +881,18 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2244,6 +2277,426 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381027</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860037533</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:27:50 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860037533</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:04:31 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:27:50 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.765228</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Deko fairocha, Kathmandu 44600 Near by Tokha SB Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>shrsuresh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>23:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L25-8</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.327917</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 23m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:24 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382665</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9840562307</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9844208629</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:24:53 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Radheradhe, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9844208629@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L61-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -598,20 +598,38 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B7" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -693,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -720,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -728,7 +746,8 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -759,6 +778,11 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -781,8 +805,11 @@
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>6</v>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -803,7 +830,10 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -826,7 +856,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -840,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2344,10 +2377,8 @@
           <t>Suresh Shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860037533</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860037533</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2362,10 +2393,8 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>9860037533</t>
-        </is>
+      <c r="U8" s="3" t="n">
+        <v>9860037533</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -2382,10 +2411,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.765228</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.765228</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2441,25 +2468,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L25-8</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.327917</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.327917</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2560,10 +2583,8 @@
           <t>Hemanta bhandari</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9840562307</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9840562307</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2578,10 +2599,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>9844208629</t>
-        </is>
+      <c r="U9" s="3" t="n">
+        <v>9844208629</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -2649,10 +2668,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2663,29 +2680,29 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>23h 42m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>23h 42m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2694,6 +2711,434 @@
       <c r="AX9" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:44 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:40 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381392</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Ambar  kumar magar</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Ambar  kumar magar</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841302840</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:39:15 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841302840</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:39:15 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.75076</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Bihanai basti, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>18:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L61-6</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -919,7 +919,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2997,10 +2997,8 @@
           <t>Ambar  kumar magar</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841302840</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841302840</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3015,10 +3013,8 @@
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>9841302840</t>
-        </is>
+      <c r="U12" s="3" t="n">
+        <v>9841302840</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -3035,10 +3031,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.75076</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.75076</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3090,25 +3084,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L61-6</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,21 +532,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -564,29 +564,29 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -600,36 +600,54 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>45.5%</t>
+      <c r="B8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -700,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -711,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -738,16 +756,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,25 +782,30 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -794,13 +818,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -808,8 +832,11 @@
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>7</v>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -825,15 +852,18 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -844,22 +874,25 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -896,7 +929,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -919,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3132,6 +3165,1070 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382962</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Biphute</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Yubraj Biphute</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9705259533</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:31 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>LTP9705259533</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:40:21 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:31 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>27.671718509307166, 85.31908851642197 GPS Coordinates Nearest: LTP003-01-4/13-L113 (28m Road) Map: C</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>9705259533@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>07:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L113-2</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>renewal wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381122</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Arbin Thakur</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Arbin Thakur</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9802100149</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:07:58 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9802100149</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:19:57 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:07:58 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.65685</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near Imadol Police Station lalitpur mahalaxmi , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>arbin.th2012@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>22:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3448</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1383657</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Shrestha</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Sujal Shrestha</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9863481720</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:33 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9863481720</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:01:37 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:33 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Near Euro School Ganesh Chowk, New Colony, Hattigauda Budhanilkantha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>sujaldon27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>01:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L59-8</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381219</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9843560015</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9818852660</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:35:16 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:53:29 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.71774</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Prime College,Pahikwo Sadak, Kathmandu 44600,27.71696, 85.30267 - Prime College,Pahikwo Sadak, Kathm</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>sayarkhadka@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>21:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.3018</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 18m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 1:52 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382043</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Budhathoki</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9803166523</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9803166523</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 07:47:21 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 01:52:46 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.705262</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near to Basantapur Sekuwa,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>budhathokimanoj12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>13:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB286</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.305828</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -877,7 +877,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3</v>
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -919,10 +919,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -935,7 +935,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -3232,10 +3232,8 @@
           <t>Yubraj Biphute</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9705259533</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9705259533</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3325,10 +3323,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3335,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3440,10 +3436,8 @@
           <t>Arbin Thakur</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9802100149</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9802100149</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3478,10 +3472,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.65685</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.65685</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3537,25 +3529,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3448</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.34480000000001</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : renewal wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3656,10 +3644,8 @@
           <t>Sujal Shrestha</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9863481720</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9863481720</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3749,10 +3735,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3763,7 +3747,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3864,10 +3848,8 @@
           <t>Kiran Khadka</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9843560015</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9843560015</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3902,10 +3884,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.71774</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.71774</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3961,25 +3941,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.3018</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.3018</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4080,10 +4056,8 @@
           <t>Manoj Budhathoki</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9803166523</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9803166523</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4118,10 +4092,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.705262</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.705262</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4177,55 +4149,471 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB286</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.305828</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.30582800000001</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 5m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>stb collection</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376366</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Dil Bahadur Shrestha</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:47:02 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841497101</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 08:58:40 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:26:11 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.64958</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Mahalaxmi-4, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>dilbdr123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L49-7</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.34428</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 39m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>7d 17h 27m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382665</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Hemanta bhandari</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9840562307</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9844208629</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 01:42:26 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:11:18 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Radheradhe, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9844208629@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>10:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L61-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 5m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX17" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -718,30 +718,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>72.2%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -756,10 +779,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -842,7 +865,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -855,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -868,31 +891,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>14</v>
+      <c r="H5" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -924,7 +975,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -934,14 +985,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -4254,20 +4305,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Dil Bahadur Shrestha</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841497101</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841497101</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4302,10 +4347,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.64958</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.64958</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4357,25 +4400,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L49-7</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.34428</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.34428</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : stb collection  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4476,10 +4515,8 @@
           <t>Hemanta bhandari</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9840562307</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9840562307</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4569,10 +4606,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4583,35 +4618,251 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 2:38 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382732</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Sumit Tamang</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Sumit Tamang</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861966412</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9861966412</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 02:36:53 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 02:38:52 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.680025</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Near by Sagarmata tole gate, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>9861966412@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L20-3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.370184</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>1d 28m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -1003,7 +1003,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4709,20 +4709,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Sumit Tamang</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861966412</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861966412</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4757,10 +4751,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.680025</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.680025</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4816,25 +4808,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L20-3</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.370184</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.37018399999999</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -859,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -919,31 +919,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>15</v>
+      <c r="H6" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -957,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -968,7 +996,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1003,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4856,6 +4884,414 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 3:17 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382760</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Tamang</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Tamang</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9843358659</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9843358659</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:07:01 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:17:16 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>imadol near bhandari marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>10:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L55-2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 10m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 3:44 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>no internet conncetion</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382964</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Poudel</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Poudel</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>8549856548</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:44:40 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9746291665</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 03:44:40 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>P9Q7+J3 Budhanilkantha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>09:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>23h 2m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -1031,7 +1031,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4951,10 +4951,8 @@
           <t>Raj Kumar Tamang</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9843358659</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9843358659</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5040,10 +5038,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -5054,7 +5050,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5155,10 +5151,8 @@
           <t>Shristi Poudel</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>8549856548</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>8549856548</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5244,10 +5238,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -5258,7 +5250,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet conncetion   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>14</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -779,10 +779,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -893,11 +893,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -934,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -947,31 +947,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>17</v>
+      <c r="H7" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1020,7 +1048,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1031,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5284,6 +5312,218 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>slow speed</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379469</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Aayush Shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Aayush Shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9849396345</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 10:48:04 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9849396345</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:40 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 04:02:11 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.67544</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Patan, Ombahal Bangalamukhi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>uraayush@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB604E</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.32756</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>5h 14m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5379,10 +5379,8 @@
           <t>Aayush Shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9849396345</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9849396345</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5417,10 +5415,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.67544</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.67544</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5472,25 +5468,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB604E</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.32756</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.32756000000001</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : slow speed  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -984,7 +984,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>4</v>
@@ -999,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5516,6 +5516,430 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 9:31 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382779</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Januka Puri</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Januka Puri</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9845865646</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:31:38 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841385524</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 03:24:10 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:31:38 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67952</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Pimbhal cooker cafe House No. 191, M8FC+WXW, Dhaugal Galli Pimbahal, Lalitpur 44700, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>14:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.30697</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 7m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 9:30 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1382482</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Bahadur KC</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Bahadur KC</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9801026714</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:30:41 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9801026714</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>29 Oct 2026 11:34:03 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>30 Oct 2026 09:30:41 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.659728</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Anu Books Store - Book store Lagankhel Satdobato Rd Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>18:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB956</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.323702</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 9h 56m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_30_Oct_2026.xlsx
@@ -1059,7 +1059,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5583,10 +5583,8 @@
           <t>Januka Puri</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9845865646</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9845865646</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5621,10 +5619,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67952</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67952</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5676,25 +5672,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.30697</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.30697000000001</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5795,10 +5787,8 @@
           <t>Kamal Bahadur KC</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9801026714</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9801026714</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5833,10 +5823,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.659728</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.659728</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5888,25 +5876,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB956</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.323702</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.323702</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade    has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
